--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:36</t>
+    <t xml:space="preserve">2026-09-09 22:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:21</t>
+    <t xml:space="preserve">2026-09-12 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:38</t>
+    <t xml:space="preserve">2026-09-24 00:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:15</t>
+    <t xml:space="preserve">2026-09-27 22:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:05</t>
+    <t xml:space="preserve">2026-09-29 10:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32.47</v>
+        <v>324.74</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>27.92</v>
+        <v>279.16</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>19.58</v>
+        <v>195.78</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14.91</v>
+        <v>149.15</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>14.83</v>
+        <v>148.26</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11.14</v>
+        <v>111.42</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>10.17</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8.66</v>
+        <v>86.61</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7.61</v>
+        <v>76.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 10:59</t>
+    <t xml:space="preserve">2026-10-01 19:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:24</t>
+    <t xml:space="preserve">2026-10-02 13:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:04</t>
+    <t xml:space="preserve">2026-10-05 07:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
